--- a/feat/phq-15/StructureDefinition-mii-pr-pro-score-blueprint.xlsx
+++ b/feat/phq-15/StructureDefinition-mii-pr-pro-score-blueprint.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:28:41+00:00</t>
+    <t>2026-07-07T06:22:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
